--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-12-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff68bfe8255
+	0x7ff68bfe82b0
+	0x7ff68bdc165d
+	0x7ff68be19a33
+	0x7ff68be19d3c
+	0x7ff68be6df67
+	0x7ff68be6ac97
+	0x7ff68be0ac29
+	0x7ff68be0ba93
+	0x7ff68c2ffff0
+	0x7ff68c2fa930
+	0x7ff68c319096
+	0x7ff68c005754
+	0x7ff68c00e6fc
+	0x7ff68bff1974
+	0x7ff68bff1b25
+	0x7ff68bfd7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff6d4a38255
+	0x7ff6d4a382b0
+	0x7ff6d481165d
+	0x7ff6d4869a33
+	0x7ff6d4869d3c
+	0x7ff6d48bdf67
+	0x7ff6d48bac97
+	0x7ff6d485ac29
+	0x7ff6d485ba93
+	0x7ff6d4d4fff0
+	0x7ff6d4d4a930
+	0x7ff6d4d69096
+	0x7ff6d4a55754
+	0x7ff6d4a5e6fc
+	0x7ff6d4a41974
+	0x7ff6d4a41b25
+	0x7ff6d4a27852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff6d4a38255
+	0x7ff6d4a382b0
+	0x7ff6d481165d
+	0x7ff6d4869a33
+	0x7ff6d4869d3c
+	0x7ff6d48bdf67
+	0x7ff6d48bac97
+	0x7ff6d485ac29
+	0x7ff6d485ba93
+	0x7ff6d4d4fff0
+	0x7ff6d4d4a930
+	0x7ff6d4d69096
+	0x7ff6d4a55754
+	0x7ff6d4a5e6fc
+	0x7ff6d4a41974
+	0x7ff6d4a41b25
+	0x7ff6d4a27852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff6d4a38255
+	0x7ff6d4a382b0
+	0x7ff6d481165d
+	0x7ff6d4869a33
+	0x7ff6d4869d3c
+	0x7ff6d48bdf67
+	0x7ff6d48bac97
+	0x7ff6d485ac29
+	0x7ff6d485ba93
+	0x7ff6d4d4fff0
+	0x7ff6d4d4a930
+	0x7ff6d4d69096
+	0x7ff6d4a55754
+	0x7ff6d4a5e6fc
+	0x7ff6d4a41974
+	0x7ff6d4a41b25
+	0x7ff6d4a27852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2027,1445 +2027,1451 @@
         </is>
       </c>
       <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 300.000
+  (Session info: chrome=143.0.7499.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb16e847
+	0x7ff7bb16e5bd
+	0x7ff7bb16c20a
+	0x7ff7bb16cbcf
+	0x7ff7bb17bb8a
+	0x7ff7bb19223f
+	0x7ff7bb19940a
+	0x7ff7bb16d375
+	0x7ff7bb191df2
+	0x7ff7bb22ab71
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
+</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>£37.39</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>£73.80</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>£37.14</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>£59.77</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>£40.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>140mm Celotex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>140mm Celotex XR4140 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£37.90</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>£37.90</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>£38.50</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>£37.94</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>£38.50</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>£37.59</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>£37.25</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>£37.79</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>£37.39</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>£73.80</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>£37.14</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>£40.35</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>£78.85</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>£40.25</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>£59.77</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>£40.04</t>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>£59.8</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>140mm Celotex</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>140mm Celotex XR4140 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£37.90</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>£37.90</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>£38.50</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>£37.94</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>£38.50</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>£37.59</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>£47.29</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>£37.25</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>£37.79</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>150mm Celotex</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>150mm Celotex XR4150 2.4m X 1.2m</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>£38.00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>£37.32</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>£37.00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>£43.58</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>£37.10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>£37.32</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>£40.35</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>£78.85</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>£40.25</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>£39.6</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>£82.06</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>£39.47</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>£59.8</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>N/L</t>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>£40.45</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>150mm Celotex</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150mm Celotex XR4150 2.4m X 1.2m</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>£38.00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>£37.32</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>£37.00</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>£43.58</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>£37.10</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>£37.32</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>165mm Celotex1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>165mm Celotex XR4165 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£660.25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>£660.25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>£660.25</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>£877.92</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>£719.88</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>£857.88</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>£690.66</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>£634.53</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Error: could not convert string to float: 'Guide'</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>xr4200pal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>200mm Celotex XR4200 2.4m x 1.2m  (Pallet of 12)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£850.25</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>£850.25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>£850.25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>£960.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>£935.88</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>£1029.48</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>£1407.24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>£867.05</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>£39.6</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>£82.06</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>£39.47</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>£40.45</t>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>£853.62</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>£1164.06</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>£1073.28</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>£852.50 Pre Sale Price-£889.80</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>165mm Celotex1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>165mm Celotex XR4165 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£660.25</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>£660.25</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>£660.25</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>£695.00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>£877.92</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>£719.88</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>£857.88</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>£690.66</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>£634.53</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Error: could not convert string to float: 'Guide'</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>xr4200pal</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>200mm Celotex XR4200 2.4m x 1.2m  (Pallet of 12)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£850.25</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>£850.25</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>£850.25</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>£895.00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>£960.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>£935.88</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>£1029.48</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>£1407.24</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>£867.05</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PL4025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Celotex PL4025 37.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£25.58</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>£25.58</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>£25.58</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>£31.50</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>£28.12</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>£26.99</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>£26.90</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>£37.39</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>£26.63</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>£25.50</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>£853.62</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>£1164.06</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>£1073.28</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>£852.50 Pre Sale Price-£889.80</t>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>£36.95</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>£68.31</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>£48.24</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>£49.22</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>£29.28 Pre Sale Price-£30.00</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PL4025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Celotex PL4025 37.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£25.58</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>£25.58</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>£25.58</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>£31.50</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>£28.12</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>£26.99</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>£26.90</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>£37.39</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>£26.63</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>£25.50</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PL4040</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Celotex PL4040 52.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£31.30</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>£31.30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>£31.30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>£38.75</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>£33.87</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>£32.99</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>£31.65</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>£32.37</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>£31.05</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>£36.95</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>£68.31</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>£48.24</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>£49.22</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>£29.28 Pre Sale Price-£30.00</t>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>£44.24</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>£79.12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>£58.53</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>£49.55</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>£35.60 Pre Sale Price-£35.83</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PL4040</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Celotex PL4040 52.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£31.30</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>£31.30</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>£31.30</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>£38.75</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>£33.87</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>£32.99</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>£31.65</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>£47.29</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>£32.37</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>£31.05</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PL4050</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Celotex PL4050 62.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£34.15</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>£34.15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>£34.15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>£39.75</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>£36.81</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>£35.99</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>£35.60</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>£49.49</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>£35.65</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>£34.10</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>£44.24</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>£79.12</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>£58.53</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>£49.55</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>£35.60 Pre Sale Price-£35.83</t>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>£52.32</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>£87.37</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>£66.08</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>£68.97</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>£38.56 Pre Sale Price-£40.83</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PL4050</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Celotex PL4050 62.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£34.15</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>£34.15</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>£34.15</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>£39.75</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>£36.81</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>£35.99</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>£35.60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>£49.49</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>£35.65</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>£34.10</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PL4060</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Celotex PL4060 72.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£38.90</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>£38.90</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>£38.90</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>£43.50</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>£41.98</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>£40.99</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>£40.48</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>£54.99</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>£40.59</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>£38.80</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>£52.32</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>£87.37</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>£66.08</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>£68.97</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>£38.56 Pre Sale Price-£40.83</t>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>£55.49</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>£92.82</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>£68.87</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>£79.88</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>£43.59 Pre Sale Price-£45.83</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PL4060</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Celotex PL4060 72.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£38.90</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>£38.90</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>£38.90</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>£43.50</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>£41.98</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>£40.99</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>£40.48</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>£54.99</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>£40.59</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>£38.80</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>celcav50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 50mm </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£41.23</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>£41.23</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>£41.23</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>£42.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>£49.6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>£43.79</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>£41.60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>£78.54</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>£43.55</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff7bb3a8255
+	0x7ff7bb3a82b0
+	0x7ff7bb18165d
+	0x7ff7bb1d9a33
+	0x7ff7bb1d9d3c
+	0x7ff7bb22df67
+	0x7ff7bb22ac97
+	0x7ff7bb1cac29
+	0x7ff7bb1cba93
+	0x7ff7bb6bfff0
+	0x7ff7bb6ba930
+	0x7ff7bb6d9096
+	0x7ff7bb3c5754
+	0x7ff7bb3ce6fc
+	0x7ff7bb3b1974
+	0x7ff7bb3b1b25
+	0x7ff7bb397852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>£55.49</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>£92.82</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>£68.87</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>£79.88</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>£43.59 Pre Sale Price-£45.83</t>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>£41.25</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>£68.43</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>£65.48</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>£60.57</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>£46.36</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>celcav50</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Celotex CW 50mm </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£41.23</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>£41.23</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>£41.23</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cw40755</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 75mm </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£41.33</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>£41.33</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>£41.33</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>£42.50</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>£49.6</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>£43.79</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>£41.60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>£78.54</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>£43.55</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>£48.04</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>£43.25</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>£41.71</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>£85.44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>£47.03</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff708328255
+	0x7ff7083282b0
+	0x7ff70810165d
+	0x7ff708159a33
+	0x7ff708159d3c
+	0x7ff7081adf67
+	0x7ff7081aac97
+	0x7ff70814ac29
+	0x7ff70814ba93
+	0x7ff70863fff0
+	0x7ff70863a930
+	0x7ff708659096
+	0x7ff708345754
+	0x7ff70834e6fc
+	0x7ff708331974
+	0x7ff708331b25
+	0x7ff708317852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>£41.25</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>£68.43</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>£65.48</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>£39.38</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>£71.62</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>£63.59</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>£60.57</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>£46.36</t>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>£68.48</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>£45.63</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cw40755</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Celotex CW 75mm </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£41.33</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>£41.33</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>£41.33</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>£42.50</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>£48.04</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>£43.25</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>£41.71</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>£85.44</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>£47.03</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>celcav85</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Celotex CW 85mm (16 Packs)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£925.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>£925.00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>£925.00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>£924.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff708328255
+	0x7ff7083282b0
+	0x7ff70810165d
+	0x7ff708159a33
+	0x7ff708159d3c
+	0x7ff7081adf67
+	0x7ff7081aac97
+	0x7ff70814ac29
+	0x7ff70814ba93
+	0x7ff70863fff0
+	0x7ff70863a930
+	0x7ff708659096
+	0x7ff708345754
+	0x7ff70834e6fc
+	0x7ff708331974
+	0x7ff708331b25
+	0x7ff708317852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>£39.38</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>£71.62</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>£63.59</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>£68.48</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>£45.63</t>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Error: could not convert string to float: 'Guide'</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>£1787.2</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>celcav85</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Celotex CW 85mm (16 Packs)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£925.00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>£925.00</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>£925.00</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>£924.00</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cw4100</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 100mm </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£40.57</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>£40.57</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>£40.57</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>£42.50</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>£46.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>£42.80</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>£40.93</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>£81.9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>£43.05</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
-	0x7fff459ae8d7
-	0x7fff46e2c53c
-</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Error: could not convert string to float: 'Guide'</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>£1787.2</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cw4100</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Celotex CW 100mm </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£40.57</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>£40.57</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>£40.57</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>£42.50</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>£46.5</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>£42.80</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>£40.93</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>£81.9</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>£43.05</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f1688255
-	0x7ff6f16882b0
-	0x7ff6f146165d
-	0x7ff6f14b9a33
-	0x7ff6f14b9d3c
-	0x7ff6f150df67
-	0x7ff6f150ac97
-	0x7ff6f14aac29
-	0x7ff6f14aba93
-	0x7ff6f199fff0
-	0x7ff6f199a930
-	0x7ff6f19b9096
-	0x7ff6f16a5754
-	0x7ff6f16ae6fc
-	0x7ff6f1691974
-	0x7ff6f1691b25
-	0x7ff6f1677852
+	0x7ff74b558255
+	0x7ff74b5582b0
+	0x7ff74b33165d
+	0x7ff74b389a33
+	0x7ff74b389d3c
+	0x7ff74b3ddf67
+	0x7ff74b3dac97
+	0x7ff74b37ac29
+	0x7ff74b37ba93
+	0x7ff74b86fff0
+	0x7ff74b86a930
+	0x7ff74b889096
+	0x7ff74b575754
+	0x7ff74b57e6fc
+	0x7ff74b561974
+	0x7ff74b561b25
+	0x7ff74b547852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
